--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/PNEUS 12_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/PNEUS 12_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,7 +472,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -495,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PNEU VIPAL TR300 17110/90 920701</t>
+          <t>PNEU VIPAL TR300 17 110/90 920701</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -503,7 +492,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -524,7 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -545,7 +532,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -566,7 +552,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -587,7 +572,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -600,15 +584,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PNEU 17 60/100</t>
+          <t>PNEU CINBORG 17 60/100</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -629,7 +612,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -650,7 +632,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -671,11 +652,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>392</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -696,11 +672,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -721,7 +692,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -742,7 +712,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -755,24 +724,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PNEU MAGGION 14 80/100 USO CAMARA</t>
+          <t>PNEU VIPAL ST600 18 80/100 920323</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>15</v>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7897046740730</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PNEU MAGGION 14 80/100 USO CAMARA</t>
+          <t>PNEU VIPAL ST300 18 80/100 920005</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -780,7 +752,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -788,12 +759,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7897046740730</t>
+          <t>7897046740921</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PNEU VIPAL ST600 80/100 920323</t>
+          <t>PNEU VIPAL TR400 17 110/90</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -801,7 +772,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -809,12 +779,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7897046740921</t>
+          <t>7897046740716</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PNEU VIPAL TR40017 110/90</t>
+          <t>PNEU VIPAL ST500 17 140/70 920321</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -822,20 +792,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>18</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>7897046740716</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PNEU VIPAL ST500 17 140/70 920321</t>
+          <t>PNEU TECHNIC 18 90/90</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -843,26 +808,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>19</v>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>7897046740884</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PNEU TECHNIC 18 90/90</t>
+          <t>PNEU VIPAL TR300 18 130/80</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>240</t>
         </is>
       </c>
     </row>
@@ -872,20 +835,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7897046740884</t>
+          <t>7897046740778</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PNEU VIPAL TR300 18 130/80</t>
+          <t>PNEU VIPAL TR30021 90/90</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -893,22 +855,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7897046740778</t>
+          <t>7897046740754</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PNEU VIPAL TR30021 90/90</t>
+          <t>PNEU VIPAL TR30019 90/90</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>350</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -918,22 +875,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7897046740754</t>
+          <t>3528702759370</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PNEU VIPAL TR30019 90/90</t>
+          <t>PNEU LEVORIM MATRIX 19 90/90</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>310</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -943,12 +895,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3528702759370</t>
+          <t>7898153873984</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PNEU LEVIRIM MATRIX 19 90/90</t>
+          <t>PNEU MAGGION 18 90/90</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -956,26 +908,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>24</v>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>7898153873816</t>
+        </is>
+      </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PNEU MAGGION 18 90/90</t>
+          <t>PNEU MAGGION 17 60/100</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>270</t>
         </is>
       </c>
     </row>
@@ -983,14 +933,10 @@
       <c r="A27" t="n">
         <v>25</v>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>7898153873816</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PNEU MAGGION 17 60/100</t>
+          <t>PNEU CINBORG 17 130/70</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -998,26 +944,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>26</v>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7898576447151</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PNEU CINBORG 17 130/70</t>
+          <t>PNEU PROTYRE 18 2.75 DIANTEIRO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>530</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1027,20 +971,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7898576447151</t>
+          <t>7898576447168</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PNEU PROTYRE 18 2.75 DIANTEIRO</t>
+          <t>PNEU PROTYRE 18 90/90 TRASEIRO</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1048,16 +991,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7898576447168</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>PNEU PROTYRE 18 90/90 TRASEIRO</t>
-        </is>
-      </c>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
